--- a/广告组数据看板0416.xlsx
+++ b/广告组数据看板0416.xlsx
@@ -551,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1796,11 +1796,19 @@
     <row r="22">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>【合计】</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr"/>
-      <c r="C22" s="19" t="inlineStr"/>
+          <t>组21 职场</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>HNN</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="inlineStr">
+        <is>
+          <t>待补充</t>
+        </is>
+      </c>
       <c r="D22" s="21" t="inlineStr">
         <is>
           <t>$28.04/5/$5.61</t>
@@ -1851,9 +1859,80 @@
           <t>$143.79/39/$3.69</t>
         </is>
       </c>
+      <c r="N22" s="26" t="inlineStr">
+        <is>
+          <t>$9.62/1/$9.62</t>
+        </is>
+      </c>
       <c r="O22" s="21" t="inlineStr">
         <is>
           <t>$936.52/214/$4.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>组22 Voyeurism</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>HZM</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>待补充</t>
+        </is>
+      </c>
+      <c r="N23" s="26" t="inlineStr">
+        <is>
+          <t>$7.86/1/$7.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>组23 工作室</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>HNN</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>待补充</t>
+        </is>
+      </c>
+      <c r="N24" s="27" t="inlineStr">
+        <is>
+          <t>$0.00/1/$0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>组24 Dom</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CHJ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>待补充</t>
+        </is>
+      </c>
+      <c r="N25" s="27" t="inlineStr">
+        <is>
+          <t>$5.40/2/$2.70</t>
         </is>
       </c>
     </row>

--- a/广告组数据看板0416.xlsx
+++ b/广告组数据看板0416.xlsx
@@ -1806,7 +1806,7 @@
       </c>
       <c r="C22" s="19" t="inlineStr">
         <is>
-          <t>待补充</t>
+          <t>scene/1977563229444947970</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>待补充</t>
+          <t>4724-understanding-dom-and-sub-roles</t>
         </is>
       </c>
       <c r="N23" s="26" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>待补充</t>
+          <t>scene/1972149814470684674</t>
         </is>
       </c>
       <c r="N24" s="27" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>待补充</t>
+          <t>scene/2013638045763465217</t>
         </is>
       </c>
       <c r="N25" s="27" t="inlineStr">

--- a/广告组数据看板0416.xlsx
+++ b/广告组数据看板0416.xlsx
@@ -551,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1933,6 +1933,18 @@
       <c r="N25" s="27" t="inlineStr">
         <is>
           <t>$5.40/2/$2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>【合计】</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>$164.21/50/$3.28</t>
         </is>
       </c>
     </row>

--- a/广告组数据看板0416.xlsx
+++ b/广告组数据看板0416.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,8 +36,15 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -97,8 +104,14 @@
         <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -120,11 +133,18 @@
         <color rgb="00AAAAAA"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -186,9 +206,62 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -636,7 +709,7 @@
           <t>4/14</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>4/15</t>
         </is>
@@ -653,79 +726,79 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>组1 Library</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>HZM</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="31" t="inlineStr">
         <is>
           <t>scene/031937</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="32" t="inlineStr">
         <is>
           <t>$13.95/3/$4.65</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="E2" s="32" t="inlineStr">
         <is>
           <t>$10.04/3/$3.35</t>
         </is>
       </c>
-      <c r="F2" s="16" t="inlineStr">
+      <c r="F2" s="32" t="inlineStr">
         <is>
           <t>$11.21/5/$2.24</t>
         </is>
       </c>
-      <c r="G2" s="16" t="inlineStr">
+      <c r="G2" s="32" t="inlineStr">
         <is>
           <t>$8.79/5/$1.76</t>
         </is>
       </c>
-      <c r="H2" s="9" t="inlineStr">
+      <c r="H2" s="32" t="inlineStr">
         <is>
           <t>$6.81/2/$3.41</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="I2" s="32" t="inlineStr">
         <is>
           <t>$10.06/0/—</t>
         </is>
       </c>
-      <c r="J2" s="16" t="inlineStr">
+      <c r="J2" s="32" t="inlineStr">
         <is>
           <t>$5.10/3/$1.70</t>
         </is>
       </c>
-      <c r="K2" s="7" t="inlineStr">
+      <c r="K2" s="32" t="inlineStr">
         <is>
           <t>$10.97/0/—</t>
         </is>
       </c>
-      <c r="L2" s="11" t="inlineStr">
+      <c r="L2" s="32" t="inlineStr">
         <is>
           <t>$10.63/1/$10.63</t>
         </is>
       </c>
-      <c r="M2" s="9" t="inlineStr">
+      <c r="M2" s="32" t="inlineStr">
         <is>
           <t>$8.68/2/$4.34</t>
         </is>
       </c>
-      <c r="N2" s="26" t="inlineStr">
+      <c r="N2" s="41" t="inlineStr">
         <is>
           <t>$18.79/2/$9.39</t>
         </is>
       </c>
-      <c r="O2" s="9" t="inlineStr">
-        <is>
-          <t>$96.24/24/$4.01</t>
+      <c r="O2" s="32" t="inlineStr">
+        <is>
+          <t>$115.03/26/$4.42</t>
         </is>
       </c>
       <c r="Q2" s="10" t="inlineStr">
@@ -735,79 +808,79 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>组2 Tonight</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="33" t="inlineStr">
         <is>
           <t>HZM</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="34" t="inlineStr">
         <is>
           <t>scene/853762</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="35" t="inlineStr">
         <is>
           <t>$14.09/2/$7.05</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="35" t="inlineStr">
         <is>
           <t>$9.79/1/$9.79</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="35" t="inlineStr">
         <is>
           <t>$9.94/1/$9.94</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="35" t="inlineStr">
         <is>
           <t>$12.55/2/$6.28</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="H3" s="35" t="inlineStr">
         <is>
           <t>$15.57/5/$3.11</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="I3" s="35" t="inlineStr">
         <is>
           <t>$14.58/2/$7.29</t>
         </is>
       </c>
-      <c r="J3" s="16" t="inlineStr">
+      <c r="J3" s="35" t="inlineStr">
         <is>
           <t>$11.66/4/$2.92</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr">
+      <c r="K3" s="35" t="inlineStr">
         <is>
           <t>$15.04/4/$3.76</t>
         </is>
       </c>
-      <c r="L3" s="11" t="inlineStr">
+      <c r="L3" s="35" t="inlineStr">
         <is>
           <t>$14.06/2/$7.03</t>
         </is>
       </c>
-      <c r="M3" s="16" t="inlineStr">
+      <c r="M3" s="35" t="inlineStr">
         <is>
           <t>$2.30/6/$0.38</t>
         </is>
       </c>
-      <c r="N3" s="26" t="inlineStr">
-        <is>
-          <t>$2.30/0/—</t>
-        </is>
-      </c>
-      <c r="O3" s="9" t="inlineStr">
-        <is>
-          <t>$119.58/29/$4.12</t>
+      <c r="N3" s="39" t="inlineStr">
+        <is>
+          <t>$2.30/1/$2.30</t>
+        </is>
+      </c>
+      <c r="O3" s="35" t="inlineStr">
+        <is>
+          <t>$121.88/30/$4.06</t>
         </is>
       </c>
       <c r="Q3" s="12" t="inlineStr">
@@ -858,6 +931,7 @@
       <c r="K4" s="13" t="inlineStr"/>
       <c r="L4" s="13" t="inlineStr"/>
       <c r="M4" s="13" t="inlineStr"/>
+      <c r="N4" s="23" t="n"/>
       <c r="O4" s="11" t="inlineStr">
         <is>
           <t>$21.26/3/$7.09</t>
@@ -870,75 +944,75 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>组4 Viennese Oyster</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>CHJ</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="34" t="inlineStr">
         <is>
           <t>3923-architecture-of-depth-m…</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr"/>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="D5" s="35" t="inlineStr"/>
+      <c r="E5" s="35" t="inlineStr">
         <is>
           <t>$9.78/3/$3.26</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="F5" s="35" t="inlineStr">
         <is>
           <t>$3.98/2/$1.99</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="35" t="inlineStr">
         <is>
           <t>$0.08/0/—</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="H5" s="35" t="inlineStr">
         <is>
           <t>$10.68/2/$5.34</t>
         </is>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="I5" s="35" t="inlineStr">
         <is>
           <t>$16.02/4/$4.01</t>
         </is>
       </c>
-      <c r="J5" s="16" t="inlineStr">
+      <c r="J5" s="35" t="inlineStr">
         <is>
           <t>$13.96/12/$1.16</t>
         </is>
       </c>
-      <c r="K5" s="16" t="inlineStr">
+      <c r="K5" s="35" t="inlineStr">
         <is>
           <t>$11.82/5/$2.36</t>
         </is>
       </c>
-      <c r="L5" s="9" t="inlineStr">
+      <c r="L5" s="35" t="inlineStr">
         <is>
           <t>$12.60/3/$4.20</t>
         </is>
       </c>
-      <c r="M5" s="9" t="inlineStr">
+      <c r="M5" s="35" t="inlineStr">
         <is>
           <t>$16.22/5/$3.24</t>
         </is>
       </c>
-      <c r="N5" s="27" t="inlineStr">
+      <c r="N5" s="39" t="inlineStr">
         <is>
           <t>$7.61/3/$2.54</t>
         </is>
       </c>
-      <c r="O5" s="16" t="inlineStr">
-        <is>
-          <t>$95.14/36/$2.64</t>
+      <c r="O5" s="35" t="inlineStr">
+        <is>
+          <t>$102.75/39/$2.63</t>
         </is>
       </c>
       <c r="Q5" s="17" t="inlineStr">
@@ -948,71 +1022,71 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="33" t="inlineStr">
         <is>
           <t>组5 30 Positions</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>CHJ</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="34" t="inlineStr">
         <is>
           <t>4690-30-adventurous-sex-posi…</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr"/>
-      <c r="E6" s="13" t="inlineStr"/>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="D6" s="35" t="inlineStr"/>
+      <c r="E6" s="35" t="inlineStr"/>
+      <c r="F6" s="35" t="inlineStr">
         <is>
           <t>$6.04/3/$2.01</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G6" s="35" t="inlineStr">
         <is>
           <t>$0.08/2/$0.04</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="35" t="inlineStr">
         <is>
           <t>$13.62/4/$3.41</t>
         </is>
       </c>
-      <c r="I6" s="16" t="inlineStr">
+      <c r="I6" s="35" t="inlineStr">
         <is>
           <t>$13.98/6/$2.33</t>
         </is>
       </c>
-      <c r="J6" s="16" t="inlineStr">
+      <c r="J6" s="35" t="inlineStr">
         <is>
           <t>$12.71/5/$2.54</t>
         </is>
       </c>
-      <c r="K6" s="9" t="inlineStr">
+      <c r="K6" s="35" t="inlineStr">
         <is>
           <t>$8.65/2/$4.33</t>
         </is>
       </c>
-      <c r="L6" s="16" t="inlineStr">
+      <c r="L6" s="35" t="inlineStr">
         <is>
           <t>$14.63/8/$1.83</t>
         </is>
       </c>
-      <c r="M6" s="16" t="inlineStr">
+      <c r="M6" s="35" t="inlineStr">
         <is>
           <t>$14.36/7/$2.05</t>
         </is>
       </c>
-      <c r="N6" s="27" t="inlineStr">
-        <is>
-          <t>$10.97/9/$1.22</t>
-        </is>
-      </c>
-      <c r="O6" s="16" t="inlineStr">
-        <is>
-          <t>$84.07/37/$2.27</t>
+      <c r="N6" s="39" t="inlineStr">
+        <is>
+          <t>$10.97/10/$1.10</t>
+        </is>
+      </c>
+      <c r="O6" s="35" t="inlineStr">
+        <is>
+          <t>$95.04/47/$2.02</t>
         </is>
       </c>
       <c r="Q6" s="18" t="inlineStr">
@@ -1022,258 +1096,258 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="33" t="inlineStr">
         <is>
           <t>组6 冰块</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>HNN</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="34" t="inlineStr">
         <is>
           <t>scene/903553</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr"/>
-      <c r="E7" s="13" t="inlineStr"/>
-      <c r="F7" s="13" t="inlineStr"/>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="D7" s="35" t="inlineStr"/>
+      <c r="E7" s="35" t="inlineStr"/>
+      <c r="F7" s="35" t="inlineStr"/>
+      <c r="G7" s="35" t="inlineStr">
         <is>
           <t>$14.76/2/$7.38</t>
         </is>
       </c>
-      <c r="H7" s="9" t="inlineStr">
+      <c r="H7" s="35" t="inlineStr">
         <is>
           <t>$8.82/2/$4.41</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I7" s="35" t="inlineStr">
         <is>
           <t>$5.47/0/—</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="J7" s="35" t="inlineStr">
         <is>
           <t>$7.61/0/—</t>
         </is>
       </c>
-      <c r="K7" s="11" t="inlineStr">
+      <c r="K7" s="35" t="inlineStr">
         <is>
           <t>$15.14/3/$5.05</t>
         </is>
       </c>
-      <c r="L7" s="11" t="inlineStr">
+      <c r="L7" s="35" t="inlineStr">
         <is>
           <t>$7.93/1/$7.93</t>
         </is>
       </c>
-      <c r="M7" s="11" t="inlineStr">
+      <c r="M7" s="35" t="inlineStr">
         <is>
           <t>$8.16/1/$8.16</t>
         </is>
       </c>
-      <c r="N7" s="27" t="inlineStr">
+      <c r="N7" s="39" t="inlineStr">
         <is>
           <t>$0.89/1/$0.89</t>
         </is>
       </c>
-      <c r="O7" s="11" t="inlineStr">
-        <is>
-          <t>$67.89/9/$7.54</t>
+      <c r="O7" s="35" t="inlineStr">
+        <is>
+          <t>$68.78/10/$6.88</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="33" t="inlineStr">
         <is>
           <t>组7 The best intimacy</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>CHJ</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="34" t="inlineStr">
         <is>
           <t>4689-mastering-anilingus-sen…</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr"/>
-      <c r="E8" s="13" t="inlineStr"/>
-      <c r="F8" s="13" t="inlineStr"/>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="D8" s="35" t="inlineStr"/>
+      <c r="E8" s="35" t="inlineStr"/>
+      <c r="F8" s="35" t="inlineStr"/>
+      <c r="G8" s="35" t="inlineStr">
         <is>
           <t>$0.05/2/$0.03</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr">
+      <c r="H8" s="35" t="inlineStr">
         <is>
           <t>$9.75/1/$9.75</t>
         </is>
       </c>
-      <c r="I8" s="16" t="inlineStr">
+      <c r="I8" s="35" t="inlineStr">
         <is>
           <t>$16.12/6/$2.69</t>
         </is>
       </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="J8" s="35" t="inlineStr">
         <is>
           <t>$7.97/3/$2.66</t>
         </is>
       </c>
-      <c r="K8" s="11" t="inlineStr">
+      <c r="K8" s="35" t="inlineStr">
         <is>
           <t>$11.30/2/$5.65</t>
         </is>
       </c>
-      <c r="L8" s="9" t="inlineStr">
+      <c r="L8" s="35" t="inlineStr">
         <is>
           <t>$15.35/4/$3.84</t>
         </is>
       </c>
-      <c r="M8" s="11" t="inlineStr">
+      <c r="M8" s="35" t="inlineStr">
         <is>
           <t>$10.95/2/$5.47</t>
         </is>
       </c>
-      <c r="N8" s="27" t="inlineStr">
+      <c r="N8" s="39" t="inlineStr">
         <is>
           <t>$12.52/6/$2.09</t>
         </is>
       </c>
-      <c r="O8" s="9" t="inlineStr">
-        <is>
-          <t>$71.49/20/$3.57</t>
+      <c r="O8" s="35" t="inlineStr">
+        <is>
+          <t>$84.01/26/$3.23</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>组8 山间</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>HNN</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="31" t="inlineStr">
         <is>
           <t>scene/680577</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr"/>
-      <c r="E9" s="13" t="inlineStr"/>
-      <c r="F9" s="13" t="inlineStr"/>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="D9" s="32" t="inlineStr"/>
+      <c r="E9" s="32" t="inlineStr"/>
+      <c r="F9" s="32" t="inlineStr"/>
+      <c r="G9" s="32" t="inlineStr">
         <is>
           <t>$10.32/2/$5.16</t>
         </is>
       </c>
-      <c r="H9" s="11" t="inlineStr">
+      <c r="H9" s="32" t="inlineStr">
         <is>
           <t>$9.39/1/$9.39</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I9" s="32" t="inlineStr">
         <is>
           <t>$9.40/0/—</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="J9" s="32" t="inlineStr">
         <is>
           <t>$5.86/0/—</t>
         </is>
       </c>
-      <c r="K9" s="7" t="inlineStr">
+      <c r="K9" s="32" t="inlineStr">
         <is>
           <t>$10.57/0/—</t>
         </is>
       </c>
-      <c r="L9" s="9" t="inlineStr">
+      <c r="L9" s="32" t="inlineStr">
         <is>
           <t>$9.34/3/$3.11</t>
         </is>
       </c>
-      <c r="M9" s="9" t="inlineStr">
+      <c r="M9" s="32" t="inlineStr">
         <is>
           <t>$4.56/1/$4.56</t>
         </is>
       </c>
-      <c r="N9" s="26" t="inlineStr">
+      <c r="N9" s="41" t="inlineStr">
         <is>
           <t>$7.07/1/$7.07</t>
         </is>
       </c>
-      <c r="O9" s="11" t="inlineStr">
-        <is>
-          <t>$59.44/7/$8.49</t>
+      <c r="O9" s="32" t="inlineStr">
+        <is>
+          <t>$66.51/8/$8.31</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="33" t="inlineStr">
         <is>
           <t>组9 金项圈</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>HNN</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="34" t="inlineStr">
         <is>
           <t>scene/578113</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr"/>
-      <c r="E10" s="13" t="inlineStr"/>
-      <c r="F10" s="13" t="inlineStr"/>
-      <c r="G10" s="13" t="inlineStr"/>
-      <c r="H10" s="9" t="inlineStr">
+      <c r="D10" s="35" t="inlineStr"/>
+      <c r="E10" s="35" t="inlineStr"/>
+      <c r="F10" s="35" t="inlineStr"/>
+      <c r="G10" s="35" t="inlineStr"/>
+      <c r="H10" s="35" t="inlineStr">
         <is>
           <t>$9.17/2/$4.59</t>
         </is>
       </c>
-      <c r="I10" s="9" t="inlineStr">
+      <c r="I10" s="35" t="inlineStr">
         <is>
           <t>$9.51/3/$3.17</t>
         </is>
       </c>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="J10" s="35" t="inlineStr">
         <is>
           <t>$5.30/0/—</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="K10" s="35" t="inlineStr">
         <is>
           <t>$14.88/1/$14.88</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="L10" s="35" t="inlineStr">
         <is>
           <t>$7.96/1/$7.96</t>
         </is>
       </c>
-      <c r="M10" s="7" t="inlineStr">
+      <c r="M10" s="35" t="inlineStr">
         <is>
           <t>$9.80/0/—</t>
         </is>
       </c>
-      <c r="N10" s="27" t="inlineStr">
+      <c r="N10" s="39" t="inlineStr">
         <is>
           <t>$7.53/4/$1.88</t>
         </is>
       </c>
-      <c r="O10" s="11" t="inlineStr">
-        <is>
-          <t>$56.62/7/$8.09</t>
+      <c r="O10" s="35" t="inlineStr">
+        <is>
+          <t>$64.15/11/$5.83</t>
         </is>
       </c>
     </row>
@@ -1323,6 +1397,7 @@
         </is>
       </c>
       <c r="M11" s="13" t="inlineStr"/>
+      <c r="N11" s="23" t="n"/>
       <c r="O11" s="11" t="inlineStr">
         <is>
           <t>$34.14/5/$6.83</t>
@@ -1375,6 +1450,7 @@
         </is>
       </c>
       <c r="M12" s="13" t="inlineStr"/>
+      <c r="N12" s="23" t="n"/>
       <c r="O12" s="11" t="inlineStr">
         <is>
           <t>$36.65/4/$9.16</t>
@@ -1382,59 +1458,59 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="33" t="inlineStr">
         <is>
           <t>组12 浴室</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="33" t="inlineStr">
         <is>
           <t>HNN</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="34" t="inlineStr">
         <is>
           <t>scene/888321</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr"/>
-      <c r="E13" s="13" t="inlineStr"/>
-      <c r="F13" s="13" t="inlineStr"/>
-      <c r="G13" s="13" t="inlineStr"/>
-      <c r="H13" s="13" t="inlineStr"/>
-      <c r="I13" s="11" t="inlineStr">
+      <c r="D13" s="35" t="inlineStr"/>
+      <c r="E13" s="35" t="inlineStr"/>
+      <c r="F13" s="35" t="inlineStr"/>
+      <c r="G13" s="35" t="inlineStr"/>
+      <c r="H13" s="35" t="inlineStr"/>
+      <c r="I13" s="35" t="inlineStr">
         <is>
           <t>$14.36/2/$7.18</t>
         </is>
       </c>
-      <c r="J13" s="16" t="inlineStr">
+      <c r="J13" s="35" t="inlineStr">
         <is>
           <t>$5.49/2/$2.75</t>
         </is>
       </c>
-      <c r="K13" s="11" t="inlineStr">
+      <c r="K13" s="35" t="inlineStr">
         <is>
           <t>$15.72/1/$15.72</t>
         </is>
       </c>
-      <c r="L13" s="11" t="inlineStr">
+      <c r="L13" s="35" t="inlineStr">
         <is>
           <t>$11.18/1/$11.18</t>
         </is>
       </c>
-      <c r="M13" s="9" t="inlineStr">
+      <c r="M13" s="35" t="inlineStr">
         <is>
           <t>$8.48/2/$4.24</t>
         </is>
       </c>
-      <c r="N13" s="27" t="inlineStr">
+      <c r="N13" s="39" t="inlineStr">
         <is>
           <t>$5.58/3/$1.86</t>
         </is>
       </c>
-      <c r="O13" s="11" t="inlineStr">
-        <is>
-          <t>$55.23/8/$6.90</t>
+      <c r="O13" s="35" t="inlineStr">
+        <is>
+          <t>$60.81/11/$5.53</t>
         </is>
       </c>
     </row>
@@ -1480,6 +1556,7 @@
         </is>
       </c>
       <c r="M14" s="13" t="inlineStr"/>
+      <c r="N14" s="23" t="n"/>
       <c r="O14" s="11" t="inlineStr">
         <is>
           <t>$28.00/4/$7.00</t>
@@ -1524,11 +1601,7 @@
           <t>$9.92/0/—</t>
         </is>
       </c>
-      <c r="N15" s="26" t="inlineStr">
-        <is>
-          <t>$6.26/0/—</t>
-        </is>
-      </c>
+      <c r="N15" s="23" t="n"/>
       <c r="O15" s="11" t="inlineStr">
         <is>
           <t>$23.41/2/$11.71</t>
@@ -1536,47 +1609,47 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="30" t="inlineStr">
         <is>
           <t>组15 Power Shift</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>HZM</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="31" t="inlineStr">
         <is>
           <t>scene/922306</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr"/>
-      <c r="E16" s="13" t="inlineStr"/>
-      <c r="F16" s="13" t="inlineStr"/>
-      <c r="G16" s="13" t="inlineStr"/>
-      <c r="H16" s="13" t="inlineStr"/>
-      <c r="I16" s="13" t="inlineStr"/>
-      <c r="J16" s="13" t="inlineStr"/>
-      <c r="K16" s="13" t="inlineStr"/>
-      <c r="L16" s="11" t="inlineStr">
+      <c r="D16" s="32" t="inlineStr"/>
+      <c r="E16" s="32" t="inlineStr"/>
+      <c r="F16" s="32" t="inlineStr"/>
+      <c r="G16" s="32" t="inlineStr"/>
+      <c r="H16" s="32" t="inlineStr"/>
+      <c r="I16" s="32" t="inlineStr"/>
+      <c r="J16" s="32" t="inlineStr"/>
+      <c r="K16" s="32" t="inlineStr"/>
+      <c r="L16" s="32" t="inlineStr">
         <is>
           <t>$12.32/2/$6.16</t>
         </is>
       </c>
-      <c r="M16" s="7" t="inlineStr">
+      <c r="M16" s="32" t="inlineStr">
         <is>
           <t>$6.97/0/—</t>
         </is>
       </c>
-      <c r="N16" s="26" t="inlineStr">
+      <c r="N16" s="41" t="inlineStr">
         <is>
           <t>$16.63/2/$8.31</t>
         </is>
       </c>
-      <c r="O16" s="11" t="inlineStr">
-        <is>
-          <t>$19.29/2/$9.64</t>
+      <c r="O16" s="32" t="inlineStr">
+        <is>
+          <t>$35.92/4/$8.98</t>
         </is>
       </c>
     </row>
@@ -1614,11 +1687,7 @@
           <t>$7.73/0/—</t>
         </is>
       </c>
-      <c r="N17" s="26" t="inlineStr">
-        <is>
-          <t>$6.28/0/—</t>
-        </is>
-      </c>
+      <c r="N17" s="23" t="n"/>
       <c r="O17" s="11" t="inlineStr">
         <is>
           <t>$24.40/2/$12.20</t>
@@ -1626,325 +1695,387 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="36" t="inlineStr">
         <is>
           <t>组17 18 Sensual</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="36" t="inlineStr">
         <is>
           <t>CHJ</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="37" t="inlineStr">
         <is>
           <t>4686-18-sensual-couch-sex-id…</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr"/>
-      <c r="E18" s="13" t="inlineStr"/>
-      <c r="F18" s="13" t="inlineStr"/>
-      <c r="G18" s="13" t="inlineStr"/>
-      <c r="H18" s="13" t="inlineStr"/>
-      <c r="I18" s="13" t="inlineStr"/>
-      <c r="J18" s="13" t="inlineStr"/>
-      <c r="K18" s="13" t="inlineStr"/>
-      <c r="L18" s="9" t="inlineStr">
+      <c r="D18" s="38" t="inlineStr"/>
+      <c r="E18" s="38" t="inlineStr"/>
+      <c r="F18" s="38" t="inlineStr"/>
+      <c r="G18" s="38" t="inlineStr"/>
+      <c r="H18" s="38" t="inlineStr"/>
+      <c r="I18" s="38" t="inlineStr"/>
+      <c r="J18" s="38" t="inlineStr"/>
+      <c r="K18" s="38" t="inlineStr"/>
+      <c r="L18" s="38" t="inlineStr">
         <is>
           <t>$8.01/2/$4.01</t>
         </is>
       </c>
-      <c r="M18" s="16" t="inlineStr">
+      <c r="M18" s="38" t="inlineStr">
         <is>
           <t>$10.91/4/$2.73</t>
         </is>
       </c>
-      <c r="N18" s="28" t="inlineStr">
+      <c r="N18" s="54" t="inlineStr">
         <is>
           <t>$6.99/2/$3.50</t>
         </is>
       </c>
-      <c r="O18" s="9" t="inlineStr">
-        <is>
-          <t>$18.92/6/$3.15</t>
+      <c r="O18" s="38" t="inlineStr">
+        <is>
+          <t>$25.91/8/$3.24</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="23" t="inlineStr">
+      <c r="A19" s="39" t="inlineStr">
         <is>
           <t>组18 红玫瑰</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B19" s="35" t="inlineStr">
         <is>
           <t>HNN</t>
         </is>
       </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="C19" s="40" t="inlineStr">
         <is>
           <t>scene/613826</t>
         </is>
       </c>
-      <c r="D19" s="25" t="inlineStr"/>
-      <c r="E19" s="25" t="inlineStr"/>
-      <c r="F19" s="25" t="inlineStr"/>
-      <c r="G19" s="25" t="inlineStr"/>
-      <c r="H19" s="25" t="inlineStr"/>
-      <c r="I19" s="25" t="inlineStr"/>
-      <c r="J19" s="25" t="inlineStr"/>
-      <c r="K19" s="25" t="inlineStr"/>
-      <c r="L19" s="25" t="inlineStr"/>
-      <c r="M19" s="16" t="inlineStr">
+      <c r="D19" s="39" t="inlineStr"/>
+      <c r="E19" s="39" t="inlineStr"/>
+      <c r="F19" s="39" t="inlineStr"/>
+      <c r="G19" s="39" t="inlineStr"/>
+      <c r="H19" s="39" t="inlineStr"/>
+      <c r="I19" s="39" t="inlineStr"/>
+      <c r="J19" s="39" t="inlineStr"/>
+      <c r="K19" s="39" t="inlineStr"/>
+      <c r="L19" s="39" t="inlineStr"/>
+      <c r="M19" s="35" t="inlineStr">
         <is>
           <t>$9.79/4/$2.45</t>
         </is>
       </c>
-      <c r="N19" s="28" t="inlineStr">
-        <is>
-          <t>$9.01/2/$4.50</t>
-        </is>
-      </c>
-      <c r="O19" s="16" t="inlineStr">
-        <is>
-          <t>$9.79/4/$2.45</t>
+      <c r="N19" s="39" t="inlineStr">
+        <is>
+          <t>$9.01/4/$2.25</t>
+        </is>
+      </c>
+      <c r="O19" s="35" t="inlineStr">
+        <is>
+          <t>$18.80/8/$2.35</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="23" t="inlineStr">
+      <c r="A20" s="41" t="inlineStr">
         <is>
           <t>组19 Top Predator's</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B20" s="32" t="inlineStr">
         <is>
           <t>HZM</t>
         </is>
       </c>
-      <c r="C20" s="24" t="inlineStr">
+      <c r="C20" s="42" t="inlineStr">
         <is>
           <t>scene/922306</t>
         </is>
       </c>
-      <c r="D20" s="25" t="inlineStr"/>
-      <c r="E20" s="25" t="inlineStr"/>
-      <c r="F20" s="25" t="inlineStr"/>
-      <c r="G20" s="25" t="inlineStr"/>
-      <c r="H20" s="25" t="inlineStr"/>
-      <c r="I20" s="25" t="inlineStr"/>
-      <c r="J20" s="25" t="inlineStr"/>
-      <c r="K20" s="25" t="inlineStr"/>
-      <c r="L20" s="25" t="inlineStr"/>
-      <c r="M20" s="16" t="inlineStr">
+      <c r="D20" s="41" t="inlineStr"/>
+      <c r="E20" s="41" t="inlineStr"/>
+      <c r="F20" s="41" t="inlineStr"/>
+      <c r="G20" s="41" t="inlineStr"/>
+      <c r="H20" s="41" t="inlineStr"/>
+      <c r="I20" s="41" t="inlineStr"/>
+      <c r="J20" s="41" t="inlineStr"/>
+      <c r="K20" s="41" t="inlineStr"/>
+      <c r="L20" s="41" t="inlineStr"/>
+      <c r="M20" s="32" t="inlineStr">
         <is>
           <t>$7.64/3/$2.55</t>
         </is>
       </c>
-      <c r="N20" s="26" t="inlineStr">
+      <c r="N20" s="41" t="inlineStr">
         <is>
           <t>$15.59/1/$15.59</t>
         </is>
       </c>
-      <c r="O20" s="16" t="inlineStr">
-        <is>
-          <t>$7.64/3/$2.55</t>
+      <c r="O20" s="32" t="inlineStr">
+        <is>
+          <t>$23.23/4/$5.81</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="23" t="inlineStr">
+      <c r="A21" s="39" t="inlineStr">
         <is>
           <t>组20 A Softer</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B21" s="35" t="inlineStr">
         <is>
           <t>CHJ</t>
         </is>
       </c>
-      <c r="C21" s="24" t="inlineStr">
+      <c r="C21" s="40" t="inlineStr">
         <is>
           <t>4763-pillow-humping-essentia…</t>
         </is>
       </c>
-      <c r="D21" s="25" t="inlineStr"/>
-      <c r="E21" s="25" t="inlineStr"/>
-      <c r="F21" s="25" t="inlineStr"/>
-      <c r="G21" s="25" t="inlineStr"/>
-      <c r="H21" s="25" t="inlineStr"/>
-      <c r="I21" s="25" t="inlineStr"/>
-      <c r="J21" s="25" t="inlineStr"/>
-      <c r="K21" s="25" t="inlineStr"/>
-      <c r="L21" s="25" t="inlineStr"/>
-      <c r="M21" s="9" t="inlineStr">
+      <c r="D21" s="39" t="inlineStr"/>
+      <c r="E21" s="39" t="inlineStr"/>
+      <c r="F21" s="39" t="inlineStr"/>
+      <c r="G21" s="39" t="inlineStr"/>
+      <c r="H21" s="39" t="inlineStr"/>
+      <c r="I21" s="39" t="inlineStr"/>
+      <c r="J21" s="39" t="inlineStr"/>
+      <c r="K21" s="39" t="inlineStr"/>
+      <c r="L21" s="39" t="inlineStr"/>
+      <c r="M21" s="35" t="inlineStr">
         <is>
           <t>$7.32/2/$3.66</t>
         </is>
       </c>
-      <c r="N21" s="27" t="inlineStr">
+      <c r="N21" s="39" t="inlineStr">
         <is>
           <t>$7.31/9/$0.81</t>
         </is>
       </c>
-      <c r="O21" s="9" t="inlineStr">
-        <is>
-          <t>$7.32/2/$3.66</t>
+      <c r="O21" s="35" t="inlineStr">
+        <is>
+          <t>$14.63/11/$1.33</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="A22" s="30" t="inlineStr">
         <is>
           <t>组21 职场</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>HNN</t>
         </is>
       </c>
-      <c r="C22" s="19" t="inlineStr">
+      <c r="C22" s="52" t="inlineStr">
         <is>
           <t>scene/1977563229444947970</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="D22" s="41" t="n"/>
+      <c r="E22" s="41" t="n"/>
+      <c r="F22" s="41" t="n"/>
+      <c r="G22" s="41" t="n"/>
+      <c r="H22" s="41" t="n"/>
+      <c r="I22" s="41" t="n"/>
+      <c r="J22" s="41" t="n"/>
+      <c r="K22" s="41" t="n"/>
+      <c r="L22" s="41" t="n"/>
+      <c r="M22" s="41" t="n"/>
+      <c r="N22" s="41" t="inlineStr">
+        <is>
+          <t>$9.62/1/$9.62</t>
+        </is>
+      </c>
+      <c r="O22" s="32" t="inlineStr">
+        <is>
+          <t>$9.62/1/$9.62</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="33" t="inlineStr">
+        <is>
+          <t>组22 Voyeurism</t>
+        </is>
+      </c>
+      <c r="B23" s="33" t="inlineStr">
+        <is>
+          <t>CHJ</t>
+        </is>
+      </c>
+      <c r="C23" s="53" t="inlineStr">
+        <is>
+          <t>735-seen-body-why-is-voyeurism</t>
+        </is>
+      </c>
+      <c r="D23" s="39" t="n"/>
+      <c r="E23" s="39" t="n"/>
+      <c r="F23" s="39" t="n"/>
+      <c r="G23" s="39" t="n"/>
+      <c r="H23" s="39" t="n"/>
+      <c r="I23" s="39" t="n"/>
+      <c r="J23" s="39" t="n"/>
+      <c r="K23" s="39" t="n"/>
+      <c r="L23" s="39" t="n"/>
+      <c r="M23" s="39" t="n"/>
+      <c r="N23" s="39" t="inlineStr">
+        <is>
+          <t>$0.00/1/$0.00</t>
+        </is>
+      </c>
+      <c r="O23" s="35" t="inlineStr">
+        <is>
+          <t>$0.00/1/$0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="33" t="inlineStr">
+        <is>
+          <t>组23 工作室</t>
+        </is>
+      </c>
+      <c r="B24" s="33" t="inlineStr">
+        <is>
+          <t>HNN</t>
+        </is>
+      </c>
+      <c r="C24" s="53" t="inlineStr">
+        <is>
+          <t>scene/1972149814470684674</t>
+        </is>
+      </c>
+      <c r="D24" s="39" t="n"/>
+      <c r="E24" s="39" t="n"/>
+      <c r="F24" s="39" t="n"/>
+      <c r="G24" s="39" t="n"/>
+      <c r="H24" s="39" t="n"/>
+      <c r="I24" s="39" t="n"/>
+      <c r="J24" s="39" t="n"/>
+      <c r="K24" s="39" t="n"/>
+      <c r="L24" s="39" t="n"/>
+      <c r="M24" s="39" t="n"/>
+      <c r="N24" s="39" t="inlineStr">
+        <is>
+          <t>$0.00/1/$0.00</t>
+        </is>
+      </c>
+      <c r="O24" s="35" t="inlineStr">
+        <is>
+          <t>$0.00/1/$0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="33" t="inlineStr">
+        <is>
+          <t>组24 Dom</t>
+        </is>
+      </c>
+      <c r="B25" s="33" t="inlineStr">
+        <is>
+          <t>CHJ</t>
+        </is>
+      </c>
+      <c r="C25" s="53" t="inlineStr">
+        <is>
+          <t>4724-understanding-dom-and-sub</t>
+        </is>
+      </c>
+      <c r="D25" s="39" t="n"/>
+      <c r="E25" s="39" t="n"/>
+      <c r="F25" s="39" t="n"/>
+      <c r="G25" s="39" t="n"/>
+      <c r="H25" s="39" t="n"/>
+      <c r="I25" s="39" t="n"/>
+      <c r="J25" s="39" t="n"/>
+      <c r="K25" s="39" t="n"/>
+      <c r="L25" s="39" t="n"/>
+      <c r="M25" s="39" t="n"/>
+      <c r="N25" s="39" t="inlineStr">
+        <is>
+          <t>$5.40/2/$2.70</t>
+        </is>
+      </c>
+      <c r="O25" s="35" t="inlineStr">
+        <is>
+          <t>$5.40/2/$2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="50" t="inlineStr">
+        <is>
+          <t>【合计】</t>
+        </is>
+      </c>
+      <c r="B26" s="50" t="inlineStr"/>
+      <c r="C26" s="50" t="inlineStr"/>
+      <c r="D26" s="51" t="inlineStr">
         <is>
           <t>$28.04/5/$5.61</t>
         </is>
       </c>
-      <c r="E22" s="21" t="inlineStr">
+      <c r="E26" s="51" t="inlineStr">
         <is>
           <t>$42.04/9/$4.67</t>
         </is>
       </c>
-      <c r="F22" s="21" t="inlineStr">
+      <c r="F26" s="51" t="inlineStr">
         <is>
           <t>$40.00/11/$3.64</t>
         </is>
       </c>
-      <c r="G22" s="21" t="inlineStr">
+      <c r="G26" s="51" t="inlineStr">
         <is>
           <t>$46.63/16/$2.91</t>
         </is>
       </c>
-      <c r="H22" s="21" t="inlineStr">
+      <c r="H26" s="51" t="inlineStr">
         <is>
           <t>$99.50/23/$4.33</t>
         </is>
       </c>
-      <c r="I22" s="21" t="inlineStr">
+      <c r="I26" s="51" t="inlineStr">
         <is>
           <t>$142.15/26/$5.47</t>
         </is>
       </c>
-      <c r="J22" s="21" t="inlineStr">
+      <c r="J26" s="51" t="inlineStr">
         <is>
           <t>$95.99/31/$3.10</t>
         </is>
       </c>
-      <c r="K22" s="21" t="inlineStr">
+      <c r="K26" s="51" t="inlineStr">
         <is>
           <t>$144.38/18/$8.02</t>
         </is>
       </c>
-      <c r="L22" s="21" t="inlineStr">
+      <c r="L26" s="51" t="inlineStr">
         <is>
           <t>$154.00/36/$4.28</t>
         </is>
       </c>
-      <c r="M22" s="21" t="inlineStr">
+      <c r="M26" s="51" t="inlineStr">
         <is>
           <t>$143.79/39/$3.69</t>
         </is>
       </c>
-      <c r="N22" s="26" t="inlineStr">
-        <is>
-          <t>$9.62/1/$9.62</t>
-        </is>
-      </c>
-      <c r="O22" s="21" t="inlineStr">
-        <is>
-          <t>$936.52/214/$4.38</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>组22 Voyeurism</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>HZM</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>4724-understanding-dom-and-sub-roles</t>
-        </is>
-      </c>
-      <c r="N23" s="26" t="inlineStr">
-        <is>
-          <t>$7.86/1/$7.86</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>组23 工作室</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>HNN</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>scene/1972149814470684674</t>
-        </is>
-      </c>
-      <c r="N24" s="27" t="inlineStr">
-        <is>
-          <t>$0.00/1/$0.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>组24 Dom</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>CHJ</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>scene/2013638045763465217</t>
-        </is>
-      </c>
-      <c r="N25" s="27" t="inlineStr">
-        <is>
-          <t>$5.40/2/$2.70</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>【合计】</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>$164.21/50/$3.28</t>
+      <c r="N26" s="23" t="inlineStr">
+        <is>
+          <t>$143.81/54/$2.66</t>
+        </is>
+      </c>
+      <c r="O26" s="51" t="inlineStr">
+        <is>
+          <t>$1080.33/268/$4.03</t>
         </is>
       </c>
     </row>
@@ -1970,6 +2101,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
